--- a/GroceryApplication/src/test/resources/testdata2.xlsx
+++ b/GroceryApplication/src/test/resources/testdata2.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8280"/>
+    <workbookView windowWidth="22188" windowHeight="9000" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
+    <sheet name="AdminUser" sheetId="2" r:id="rId2"/>
+    <sheet name="ManageNews" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,12 +29,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="5">
   <si>
     <t>admin</t>
   </si>
   <si>
     <t>user</t>
+  </si>
+  <si>
+    <t>preenu</t>
+  </si>
+  <si>
+    <t>preenu1</t>
+  </si>
+  <si>
+    <t>Today News</t>
   </si>
 </sst>
 </file>
@@ -1224,4 +1235,41 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>